--- a/astro-site/public/dl/fine-dining-checklist-templates/BONUS-02-fine-dining-annual-calendar.xlsx
+++ b/astro-site/public/dl/fine-dining-checklist-templates/BONUS-02-fine-dining-annual-calendar.xlsx
@@ -810,12 +810,12 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Graduations in full swing + Mother's Day (2nd Sunday): two of the fullest midday services of the year. Memorial Day (last Monday). Cherries, strawberries, loquats. Green asparagus. Bluefin tuna (start of season). Prep for the summer menu change.</t>
+          <t>Graduations in full swing + Mother's Day (2nd Sunday): two of the fullest midday services of the year. Memorial Day (last Monday). Strawberries, asparagus, morels, ramps, soft-shell crab (start of season). Prep for the summer menu change.</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Bluefin tuna, cherries, asparagus</t>
+          <t>Morels, ramps, asparagus</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>SUMMER MENU CHANGE. Last graduations and weddings of the season. Seasonal tomatoes, peach, apricot. Signature gazpachos and cold soups. Father's Day (3rd Sunday). Patio / outdoor dinners.</t>
+          <t>SUMMER MENU CHANGE. Last graduations and weddings of the season. Seasonal tomatoes, peach, apricot. Signature chilled soups. Father's Day (3rd Sunday). Patio / outdoor dinners.</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Figs, watermelon, oily fish</t>
+          <t>Heirloom tomatoes, corn, stone fruit</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
